--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/ValueSet-as-vs-type-etablissement.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/ValueSet-as-vs-type-etablissement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:13:23+00:00</t>
+    <t>2026-06-19T14:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/ValueSet-as-vs-type-etablissement.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/ValueSet-as-vs-type-etablissement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:20:56+00:00</t>
+    <t>2026-06-16T14:13:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
